--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XI-XX/FRACC XIX/LTAIPT_A63F19.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XI-XX/FRACC XIX/LTAIPT_A63F19.xlsx
@@ -197,47 +197,47 @@
     <t>Tipo de servicio (catálogo)</t>
   </si>
   <si>
-    <t>Tipo de usuario y/o población objetivo</t>
-  </si>
-  <si>
-    <t>Descripción del servicio</t>
+    <t>Tipo de población usuaria y/o población objetivo (Redactados con perspectiva de género)</t>
+  </si>
+  <si>
+    <t>Descripción del objetivo del servicio (Redactado con perspectiva de género)</t>
   </si>
   <si>
     <t>Modalidad del servicio</t>
   </si>
   <si>
-    <t>Enumerar y detallar los requisitos</t>
-  </si>
-  <si>
-    <t>Documentos requeridos, en su caso</t>
+    <t>Enumerar y detallar los requisitos (Redactados con perspectiva de género)</t>
+  </si>
+  <si>
+    <t>Documentos requeridos, en su caso (Redactados con perspectiva de género)</t>
   </si>
   <si>
     <t>Hipervínculo a los formatos respectivo(s) publicado(s) en medio oficial</t>
   </si>
   <si>
-    <t>Última fecha de publicación del formato en el medio de difusión oficial</t>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 02/07/2021 -&gt; Última fecha de publicación del formato en el medio de difusión oficial</t>
   </si>
   <si>
     <t>Tiempo de respuesta</t>
   </si>
   <si>
-    <t>Plazo con el que cuenta el sujeto obligado para prevenir al solicitante</t>
-  </si>
-  <si>
-    <t>Plazo con el que cuenta el solicitante para cumplir con la prevención</t>
-  </si>
-  <si>
-    <t>Vigencia de los avisos, permisos, licencias, autorizaciones, registros y demás resoluciones que se emitan</t>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 02/07/2021 -&gt; Plazo con el que cuenta el sujeto obligado para prevenir al solicitante</t>
+  </si>
+  <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 02/07/2021 -&gt; Plazo con el que cuenta el solicitante para cumplir con la prevención</t>
+  </si>
+  <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 02/07/2021 -&gt; Vigencia de los avisos, permisos, licencias, autorizaciones, registros y demás resoluciones que se emitan</t>
   </si>
   <si>
     <t>Área en la que se proporciona el servicio y los datos de contacto 
 Tabla_436112</t>
   </si>
   <si>
-    <t>Objetivo de la inspección o verificación, en caso de que se requiera para llevar a cabo el servicio</t>
-  </si>
-  <si>
-    <t>Monto de los derechos o aprovechamientos aplicables, en su caso, o la forma de determinar dicho monto, así como las alternativas para realizar el pago. En su caso, especificar que es gratuito</t>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 02/07/2021 -&gt; Objetivo de la inspección o verificación, en caso de que se requiera para llevar a cabo el servicio</t>
+  </si>
+  <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 02/07/2021 -&gt; Monto de los derechos o aprovechamientos aplicables, en su caso, o la forma de determinar dicho monto, así como las alternativas para realizar el pago. En su caso, especificar que es gratuito</t>
   </si>
   <si>
     <t>Sustento legal para su cobro</t>
@@ -249,13 +249,13 @@
     <t>Fundamento jurídico-administrativo del servicio</t>
   </si>
   <si>
-    <t>Derechos del usuario ante la negativa o la falta</t>
-  </si>
-  <si>
-    <t>Información que deberá conservar para fines de acreditación, inspección y verificación con motivo del servicio</t>
-  </si>
-  <si>
-    <t>Información adicional del servicio, en su caso</t>
+    <t>Derechos de la población usuaria ante la negativa o la falta ante la prestación del servicio (Redactados con perspectiva de género)</t>
+  </si>
+  <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 02/07/2021 -&gt; Información que deberá conservar para fines de acreditación, inspección y verificación con motivo del servicio</t>
+  </si>
+  <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 02/07/2021 -&gt; Información adicional del servicio, en su caso (Redactada con perspectiva de género)</t>
   </si>
   <si>
     <t>Otro medio que permita el envío de consultas y documentos 
@@ -281,208 +281,208 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>302174FC951A8A57DF01BF98CAB07BDC</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>29CEE3A190BC15C4B6C891D6CDB578E4</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/03/2023</t>
+  </si>
+  <si>
+    <t>Examen a Título de Suficiencia</t>
+  </si>
+  <si>
+    <t>Directo</t>
+  </si>
+  <si>
+    <t>Alumnos del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Instrumento aplicado al alumno, que ha reprobado la evaluación extraordinaria, comprenderá todo el programa y el instrumento será elaborado por el docente del campo disciplinar</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>Pago de Derechos, Productos y Aprovechamientos</t>
+  </si>
+  <si>
+    <t>Solicitud de examen en su plantel</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202022/Subdireccion%20Servicios%20Educativos/1er_Trimestre/EXAMEN%20A%20TITULO%20DE%20SUFICIENCIA.pdf</t>
+  </si>
+  <si>
+    <t>09/05/2022</t>
+  </si>
+  <si>
+    <t>Diez días hábiles</t>
+  </si>
+  <si>
+    <t>Ver nota</t>
+  </si>
+  <si>
+    <t>6251324</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo III El Gobierno del Colegio de Bachilleres del Estado de Tlaxcala Artículo 12 Fracción II</t>
+  </si>
+  <si>
+    <t>Instituciones bancarias (Bancomer, Santander, HSBC, Scotiabank, Banorte, Citibanamex) Pago de Servicios Banca Electrónica Clientes Bancomer / HSBC, Transferencia electrónica de otros bancos (Bancomer, HSBC), Tiendas ANTAD (Chedraui, Farmacias del Ahorro, Soriana, Multired Global, Extra, Transfer, Bodega Aurrera, Walmart, SAM´S Club, Superama, Elektra, Banco Azteca) Receptoras de pago con cobro de comisión (Telecomm, HSBC RAP 2900, Oxxo)</t>
+  </si>
+  <si>
+    <t>Reglamento General de la Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo Décimo de los alumnos Artículo 55 Fracción II</t>
+  </si>
+  <si>
+    <t>Queja ante la Contraloría del Ejecutivo del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>http://www.tlaxcalaenlinea.gob.mx</t>
+  </si>
+  <si>
+    <t>Dirección Académica</t>
+  </si>
+  <si>
+    <t>20/04/2023</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 01 de enero de 2023 al 31 de marzo de 2023, el Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Examen a Título de Suficiencia). Durante el periodo del 01 de enero de 2023 al 31 de marzo de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Vigencia de los avisos, permisos, licencias, autorizaciones, registros y demás resoluciones que se emitan; Objetivo de la inspección o verificación, en caso de que se requiera para llevar a cabo el servicio; Información que deberá conservar para fines de acreditación, inspección y verificación con motivo del servicio; Otro medio que permita el envío de consultas y documentos.</t>
+  </si>
+  <si>
+    <t>1F03236B8AA0C9FF18C966AA0B90F3EF</t>
+  </si>
+  <si>
+    <t>Reinscripción por Semestre</t>
+  </si>
+  <si>
+    <t>Alumnos regulares del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Servicio que permite formalizar la reinscripción de segundo a sexto semestre a los planteles del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Ser alumno regular, no adeudar más de tres Unidades de Aprendizaje Curricular del Plan de Estudios del Colegio de Bachilleres del Estado de Tlaxcala, boleta de estudios del último semestre que concluyó el estudiante</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202022/Subdireccion%20Servicios%20Educativos/1er_Trimestre/REINSCRIPCION%20POR%20SEMESTRE.pdf</t>
+  </si>
+  <si>
+    <t>Un día hábil</t>
+  </si>
+  <si>
+    <t>6251328</t>
+  </si>
+  <si>
+    <t>614</t>
+  </si>
+  <si>
+    <t>Constitución Política de los Estados Unidos Mexicanos Título Primero Capítulo I de los Derechos Humanos y sus Garantías Artículo 3. Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo I personalidad y objetivos Artículo 2 Fracción II. Reglamento General de la Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo Décimo de los alumnos Artículo 50</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 01 de enero de 2023 al 31 de marzo de 2023, el Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Reinscripción por Semestre). Durante el periodo del 01 de enero de 2023 al 31 de marzo de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Vigencia de los avisos, permisos, licencias, autorizaciones, registros y demás resoluciones que se emitan; Objetivo de la inspección o verificación, en caso de que se requiera para llevar a cabo el servicio; Información que deberá conservar para fines de acreditación, inspección y verificación con motivo del servicio; Otro medio que permita el envío de consultas y documentos.</t>
+  </si>
+  <si>
+    <t>06B58784EDAFCF7394A6966238AA7C77</t>
+  </si>
+  <si>
+    <t>Inscripción a Ciclo Escolar</t>
+  </si>
+  <si>
+    <t>Aspirantes seleccionados para ingresar a planteles del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Proceso mediante el cual, se formaliza el acceso de un educando, al primer periodo escolar</t>
+  </si>
+  <si>
+    <t>Acta de Nacimiento (original y copia), seis fotografías tamaño infantil (blanco y negro) fondo blanco, frente y oídos descubiertos, hombres sin bigote y sin barba, mujeres sin aretes y sin maquillaje, Certificado de Secundaria (original y copia), Clave Única de Registro de Población (original y copia), Certificado Médico expedido por el Sector Salud Secretaría de Salud, Instituto de Seguridad y Servicios Sociales de los Trabajadores del Estado o Instituto Mexicano del Seguro Social, con biometría hemática, copia de comprobante de domicilio</t>
+  </si>
+  <si>
+    <t>6251327</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 01 de enero de 2023 al 31 de marzo de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no genera el formato Inscripción a Ciclo Escolar.  El Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Inscripción a Ciclo Escolar). Durante el periodo del 01 de enero de 2023 al 31 de marzo de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Vigencia de los avisos, permisos, licencias, autorizaciones, registros y demás resoluciones que se emitan; Objetivo de la inspección o verificación, en caso de que se requiera para llevar a cabo el servicio; Información que deberá conservar para fines de acreditación, inspección y verificación con motivo del servicio; Otro medio que permita el envío de consultas y documentos.</t>
+  </si>
+  <si>
+    <t>0B66A892373FC579BE4613DD6D523F6F</t>
+  </si>
+  <si>
+    <t>Ficha de Examen de Selección</t>
+  </si>
+  <si>
+    <t>Aspirantes a ingresar a planteles del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Documento que permite participar en el proceso de selección para ingresar a un plantel del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Solicitud de aspirante, copia de Acta de Nacimiento, dos fotografías tamaño infantil (blanco y negro) fondo blanco, frente y oídos descubiertos, hombres sin bigote y sin barba, mujeres sin aretes y sin maquillaje, copia de Certificado de Secundaria o constancia de que cursa el tercer año, copias de boletas de primero y segundo año de Secundaria</t>
+  </si>
+  <si>
+    <t>6251326</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Constitución Política de los Estados Unidos Mexicanos Título Primero Capítulo I de los Derechos Humanos y sus Garantías Artículo 3. Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo I personalidad y objetivos Artículo 2 Fracción II</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 01 de enero de 2023 al 31 de marzo de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no genera el formato Ficha de Examen de Selección. El Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Ficha de Examen de Selección). Durante el periodo del 01 de enero de 2023 al 31 de marzo de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Vigencia de los avisos, permisos, licencias, autorizaciones, registros y demás resoluciones que se emitan; Objetivo de la inspección o verificación, en caso de que se requiera para llevar a cabo el servicio; Información que deberá conservar para fines de acreditación, inspección y verificación con motivo del servicio; Otro medio que permita el envío de consultas y documentos.</t>
+  </si>
+  <si>
+    <t>4927D43EB38C2ABEF524657ADE092C67</t>
+  </si>
+  <si>
+    <t>Examen Extraordinario</t>
+  </si>
+  <si>
+    <t>Instrumento aplicado al alumno que ha reprobado la evaluación ordinaria, solo comprenderá los periodos parciales no acreditados y el instrumento será elaborado por el docente del campo disciplinar</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202022/Subdireccion%20Servicios%20Educativos/1er_Trimestre/EXAMEN%20EXTRAORDINARIO.pdf</t>
+  </si>
+  <si>
+    <t>6251325</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 01 de enero de 2023 al 31 de marzo de 2023, el Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Examen Extraordinario). Durante el periodo del 01 de enero de 2023 al 31 de marzo de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Vigencia de los avisos, permisos, licencias, autorizaciones, registros y demás resoluciones que se emitan; Objetivo de la inspección o verificación, en caso de que se requiera para llevar a cabo el servicio; Información que deberá conservar para fines de acreditación, inspección y verificación con motivo del servicio; Otro medio que permita el envío de consultas y documentos.</t>
+  </si>
+  <si>
+    <t>EDE394401F34CD17C9C5ECB8BA1F36C7</t>
   </si>
   <si>
     <t>Derecho a Laboratorio</t>
   </si>
   <si>
-    <t>Directo</t>
-  </si>
-  <si>
-    <t>Alumnos del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
     <t>Uso de las instalaciones de los laboratorios en los planteles del Colegio de Bachilleres del Estado de Tlaxcala</t>
   </si>
   <si>
-    <t>Presencial</t>
-  </si>
-  <si>
     <t>Pago de Derecho a Laboratorio</t>
   </si>
   <si>
     <t>Ficha de Pago</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>Un día hábil</t>
-  </si>
-  <si>
-    <t>Ver nota</t>
-  </si>
-  <si>
-    <t>4826103</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo III El Gobierno del Colegio de Bachilleres del Estado de Tlaxcala Artículo 12 Fracción II</t>
-  </si>
-  <si>
-    <t>Instituciones bancarias (Bancomer, Santander, HSBC, Scotiabank, Banorte, Citibanamex) Pago de Servicios Banca Electrónica Clientes Bancomer / HSBC, Transferencia electrónica de otros bancos (Bancomer, HSBC), Tiendas ANTAD (Chedraui, Farmacias del Ahorro, Soriana, Multired Global, Extra, Transfer, Bodega Aurrera, Walmart, SAM´S Club, Superama, Elektra, Banco Azteca) Receptoras de pago con cobro de comisión (Telecomm, HSBC RAP 2900, Oxxo)</t>
+    <t>6251329</t>
   </si>
   <si>
     <t>Reglamento General de la Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo Décimo de los alumnos Artículo 55 Fracción VIII</t>
   </si>
   <si>
-    <t>Queja ante la Contraloría del Ejecutivo del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>http://www.tlaxcalaenlinea.gob.mx</t>
-  </si>
-  <si>
-    <t>Dirección Académica</t>
-  </si>
-  <si>
-    <t>13/01/2023</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no genera el formato Derecho a Laboratorio. El Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Derecho a Laboratorio). Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Vigencia de los avisos, permisos, licencias, autorizaciones, registros y demás resoluciones que se emitan; Objetivo de la inspección o verificación, en caso de que se requiera para llevar a cabo el servicio; Información que deberá conservar para fines de acreditación, inspección y verificación con motivo del servicio; Otro medio que permita el envío de consultas y documentos.</t>
-  </si>
-  <si>
-    <t>2F839B7771C5E631A981EA0528FE7949</t>
-  </si>
-  <si>
-    <t>Examen Extraordinario</t>
-  </si>
-  <si>
-    <t>Instrumento aplicado al alumno que ha reprobado la evaluación ordinaria, solo comprenderá los periodos parciales no acreditados y el instrumento será elaborado por el docente del campo disciplinar</t>
-  </si>
-  <si>
-    <t>Pago de Derechos, Productos y Aprovechamientos</t>
-  </si>
-  <si>
-    <t>Solicitud de examen en su plantel</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202022/Subdireccion%20Servicios%20Educativos/1er_Trimestre/EXAMEN%20EXTRAORDINARIO.pdf</t>
-  </si>
-  <si>
-    <t>09/05/2022</t>
-  </si>
-  <si>
-    <t>Diez días hábiles</t>
-  </si>
-  <si>
-    <t>4826099</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>Reglamento General de la Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo Décimo de los alumnos Artículo 55 Fracción II</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Examen Extraordinario). Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Vigencia de los avisos, permisos, licencias, autorizaciones, registros y demás resoluciones que se emitan; Objetivo de la inspección o verificación, en caso de que se requiera para llevar a cabo el servicio; Información que deberá conservar para fines de acreditación, inspección y verificación con motivo del servicio; Otro medio que permita el envío de consultas y documentos.</t>
-  </si>
-  <si>
-    <t>5C1731CD147E2EB23675ADE942092320</t>
-  </si>
-  <si>
-    <t>Examen a Título de Suficiencia</t>
-  </si>
-  <si>
-    <t>Instrumento aplicado al alumno, que ha reprobado la evaluación extraordinaria, comprenderá todo el programa y el instrumento será elaborado por el docente del campo disciplinar</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202022/Subdireccion%20Servicios%20Educativos/1er_Trimestre/EXAMEN%20A%20TITULO%20DE%20SUFICIENCIA.pdf</t>
-  </si>
-  <si>
-    <t>4826098</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Examen a Título de Suficiencia). Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Vigencia de los avisos, permisos, licencias, autorizaciones, registros y demás resoluciones que se emitan; Objetivo de la inspección o verificación, en caso de que se requiera para llevar a cabo el servicio; Información que deberá conservar para fines de acreditación, inspección y verificación con motivo del servicio; Otro medio que permita el envío de consultas y documentos.</t>
-  </si>
-  <si>
-    <t>8002DE24AE20AAEC46B26AB181CFC5B6</t>
-  </si>
-  <si>
-    <t>Reinscripción por Semestre</t>
-  </si>
-  <si>
-    <t>Alumnos regulares del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Servicio que permite formalizar la reinscripción de segundo a sexto semestre a los planteles del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Ser alumno regular, no adeudar más de tres Unidades de Aprendizaje Curricular del Plan de Estudios del Colegio de Bachilleres del Estado de Tlaxcala, boleta de estudios del último semestre que concluyó el estudiante</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202022/Subdireccion%20Servicios%20Educativos/1er_Trimestre/REINSCRIPCION%20POR%20SEMESTRE.pdf</t>
-  </si>
-  <si>
-    <t>4826102</t>
-  </si>
-  <si>
-    <t>614</t>
-  </si>
-  <si>
-    <t>Constitución Política de los Estados Unidos Mexicanos Título Primero Capítulo I de los Derechos Humanos y sus Garantías Artículo 3. Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo I personalidad y objetivos Artículo 2 Fracción II. Reglamento General de la Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo Décimo de los alumnos Artículo 50</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Reinscripción por Semestre). Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Vigencia de los avisos, permisos, licencias, autorizaciones, registros y demás resoluciones que se emitan; Objetivo de la inspección o verificación, en caso de que se requiera para llevar a cabo el servicio; Información que deberá conservar para fines de acreditación, inspección y verificación con motivo del servicio; Otro medio que permita el envío de consultas y documentos.</t>
-  </si>
-  <si>
-    <t>6629557A11EEB21F3D5154915A1C4340</t>
-  </si>
-  <si>
-    <t>Inscripción a Ciclo Escolar</t>
-  </si>
-  <si>
-    <t>Aspirantes seleccionados para ingresar a planteles del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Proceso mediante el cual, se formaliza el acceso de un educando, al primer periodo escolar</t>
-  </si>
-  <si>
-    <t>Acta de Nacimiento (original y copia), seis fotografías tamaño infantil (blanco y negro) fondo blanco, frente y oídos descubiertos, hombres sin bigote y sin barba, mujeres sin aretes y sin maquillaje, Certificado de Secundaria (original y copia), Clave Única de Registro de Población (original y copia), Certificado Médico expedido por el Sector Salud Secretaría de Salud, Instituto de Seguridad y Servicios Sociales de los Trabajadores del Estado o Instituto Mexicano del Seguro Social, con biometría hemática, copia de comprobante de domicilio</t>
-  </si>
-  <si>
-    <t>4826101</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no genera el formato Inscripción a Ciclo Escolar.  El Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Inscripción a Ciclo Escolar). Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Vigencia de los avisos, permisos, licencias, autorizaciones, registros y demás resoluciones que se emitan; Objetivo de la inspección o verificación, en caso de que se requiera para llevar a cabo el servicio; Información que deberá conservar para fines de acreditación, inspección y verificación con motivo del servicio; Otro medio que permita el envío de consultas y documentos.</t>
-  </si>
-  <si>
-    <t>C5DE8B01335201936DAA2CC05BA429EC</t>
-  </si>
-  <si>
-    <t>Ficha de Examen de Selección</t>
-  </si>
-  <si>
-    <t>Aspirantes a ingresar a planteles del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Documento que permite participar en el proceso de selección para ingresar a un plantel del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Solicitud de aspirante, copia de Acta de Nacimiento, dos fotografías tamaño infantil (blanco y negro) fondo blanco, frente y oídos descubiertos, hombres sin bigote y sin barba, mujeres sin aretes y sin maquillaje, copia de Certificado de Secundaria o constancia de que cursa el tercer año, copias de boletas de primero y segundo año de Secundaria</t>
-  </si>
-  <si>
-    <t>4826100</t>
-  </si>
-  <si>
-    <t>Constitución Política de los Estados Unidos Mexicanos Título Primero Capítulo I de los Derechos Humanos y sus Garantías Artículo 3. Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo I personalidad y objetivos Artículo 2 Fracción II</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no genera el formato Ficha de Examen de Selección. El Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Ficha de Examen de Selección). Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Vigencia de los avisos, permisos, licencias, autorizaciones, registros y demás resoluciones que se emitan; Objetivo de la inspección o verificación, en caso de que se requiera para llevar a cabo el servicio; Información que deberá conservar para fines de acreditación, inspección y verificación con motivo del servicio; Otro medio que permita el envío de consultas y documentos.</t>
+    <t>Durante el periodo del 01 de enero de 2023 al 31 de marzo de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no genera el formato Derecho a Laboratorio. El Colegio de Bachilleres del Estado de Tlaxcala cuenta con la siguiente información, misma que puede ser consultada en el hipervínculo http://www.tlaxcalaenlinea.gob.mx  (Los pasos a seguir para la consulta, son los siguientes: 1.- Clic en el ícono de Educación, 2.- En la Leyenda Tipo de Trámite, seleccionar: Estatal, 4.- Dependencia: Colegio de Bachilleres del Estado de Tlaxcala, 5.- Área/Dirección: Ver todos, 6.- Clic en el ícono Buscar, 7.- Seleccionar: Derecho a Laboratorio). Durante el periodo del 01 de enero de 2023 al 31 de marzo de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no cuenta con la siguiente información: Plazo con el que cuenta el sujeto obligado para prevenir al solicitante; Plazo con el que cuenta el solicitante para cumplir con la prevención; Vigencia de los avisos, permisos, licencias, autorizaciones, registros y demás resoluciones que se emitan; Objetivo de la inspección o verificación, en caso de que se requiera para llevar a cabo el servicio; Información que deberá conservar para fines de acreditación, inspección y verificación con motivo del servicio; Otro medio que permita el envío de consultas y documentos.</t>
   </si>
   <si>
     <t>Indirecto</t>
@@ -599,7 +599,7 @@
     <t>Horario de atención (días y horas)</t>
   </si>
   <si>
-    <t>2A1D5DA19F0D1271052A7F08F7A8D290</t>
+    <t>7CA82EEA6945FB473BF6D2E9A102CDA5</t>
   </si>
   <si>
     <t>Control Escolar de cada uno de los 24 planteles del Colegio de Bachilleres del Estado de Tlaxcala</t>
@@ -638,19 +638,19 @@
     <t>Lunes a viernes de 8:30 a 17:30 horas</t>
   </si>
   <si>
-    <t>6E2E3971202728F2447B6A77418482F0</t>
-  </si>
-  <si>
-    <t>6E2E3971202728F2830EAFCE6AE820F2</t>
-  </si>
-  <si>
-    <t>1DB5EF0278BE8951CC2A1BD5AFAB7551</t>
-  </si>
-  <si>
-    <t>1DB5EF0278BE89513102F024CF06847B</t>
-  </si>
-  <si>
-    <t>1DB5EF0278BE8951D2E222C79461AAD8</t>
+    <t>0B7790770B910950EA3ADEB4ED2AB677</t>
+  </si>
+  <si>
+    <t>0B7790770B910950C37DB918CB53D5ED</t>
+  </si>
+  <si>
+    <t>7CA82EEA6945FB4774EA66DD67E0865D</t>
+  </si>
+  <si>
+    <t>7CA82EEA6945FB477D2556D5BA7ED27A</t>
+  </si>
+  <si>
+    <t>0B7790770B910950D0B96CEBBD7A37EB</t>
   </si>
   <si>
     <t>Corredor</t>
@@ -995,22 +995,22 @@
     <t>Clave de la localidad</t>
   </si>
   <si>
-    <t>2A1D5DA19F0D1271CBBCFE72F01C6613</t>
-  </si>
-  <si>
-    <t>1DB5EF0278BE895108FAB57FF88A904B</t>
-  </si>
-  <si>
-    <t>6E2E3971202728F2898CC478BE3B6BD4</t>
-  </si>
-  <si>
-    <t>1DB5EF0278BE8951B5B62BA12A2ADA7D</t>
-  </si>
-  <si>
-    <t>1DB5EF0278BE895145C747F571E681BA</t>
-  </si>
-  <si>
-    <t>1DB5EF0278BE8951DB16F110E3826113</t>
+    <t>7CA82EEA6945FB473E48FB854BB45514</t>
+  </si>
+  <si>
+    <t>0B7790770B9109502870A931F8180E07</t>
+  </si>
+  <si>
+    <t>0B7790770B9109508F3A10CB17873D1B</t>
+  </si>
+  <si>
+    <t>0B7790770B910950C47F3FB98E2F2B57</t>
+  </si>
+  <si>
+    <t>7CA82EEA6945FB472A5C36BE6065981C</t>
+  </si>
+  <si>
+    <t>0B7790770B91095051149E63D307463E</t>
   </si>
   <si>
     <t>Viaducto</t>
@@ -1100,7 +1100,7 @@
     <t>Código Postal</t>
   </si>
   <si>
-    <t>2A1D5DA19F0D1271E98C79D6EDE3AB6B</t>
+    <t>7CA82EEA6945FB47EB36CB75F3ABDAD9</t>
   </si>
   <si>
     <t>01 246 465 0900 Ext. 2113,2114,2139</t>
@@ -1124,19 +1124,19 @@
     <t>90600</t>
   </si>
   <si>
-    <t>1DB5EF0278BE895116E1F6C6D1576AC8</t>
-  </si>
-  <si>
-    <t>6E2E3971202728F2169D49CD45840D4D</t>
-  </si>
-  <si>
-    <t>2A1D5DA19F0D1271F15764F5C10D1A84</t>
-  </si>
-  <si>
-    <t>1DB5EF0278BE89517F5690E3B3052685</t>
-  </si>
-  <si>
-    <t>1DB5EF0278BE895156EC2B562714BF2F</t>
+    <t>0B7790770B910950408EF6A238305A8C</t>
+  </si>
+  <si>
+    <t>0B7790770B9109508D91DDC0CDC835D9</t>
+  </si>
+  <si>
+    <t>0B7790770B9109503D3C8C2576927ADE</t>
+  </si>
+  <si>
+    <t>7CA82EEA6945FB4764B606A18C7590CA</t>
+  </si>
+  <si>
+    <t>B7B2F0188F9BF024D91AADE69993828C</t>
   </si>
 </sst>
 </file>
@@ -1544,22 +1544,22 @@
     <col min="7" max="7" width="84.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="168.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="63.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="255" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="151.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="59.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="104" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="59.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="58.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="89" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="103.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="102.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="133.140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="55.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="81.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="162.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="126" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="206.28515625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="132" bestFit="1" customWidth="1"/>
     <col min="22" max="23" width="255" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="52.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="93.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="110.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="137.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="116.5703125" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="52.140625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="35.85546875" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="80.7109375" bestFit="1" customWidth="1"/>
@@ -1975,72 +1975,72 @@
         <v>90</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T8" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z8" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA8" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="W8" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="X8" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="Y8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AA8" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="AB8" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AC8" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AD8" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AE8" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AF8" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG8" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:33" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>80</v>
@@ -2052,96 +2052,96 @@
         <v>82</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>84</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>87</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T9" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="X9" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z9" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA9" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="W9" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="X9" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="Y9" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z9" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AA9" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="AB9" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AC9" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AD9" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AE9" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AF9" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG9" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:33" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>80</v>
@@ -2153,96 +2153,96 @@
         <v>82</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>84</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>87</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Y10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Z10" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AA10" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AB10" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AC10" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AD10" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AE10" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AF10" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG10" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:33" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>80</v>
@@ -2254,70 +2254,70 @@
         <v>82</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>84</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>87</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R11" s="3" t="s">
         <v>128</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T11" s="3" t="s">
         <v>129</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="V11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="W11" s="3" t="s">
         <v>130</v>
       </c>
       <c r="X11" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Y11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Z11" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AA11" s="3" t="s">
         <v>128</v>
@@ -2326,16 +2326,16 @@
         <v>128</v>
       </c>
       <c r="AC11" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AD11" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AE11" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AF11" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG11" s="3" t="s">
         <v>131</v>
@@ -2361,82 +2361,82 @@
         <v>84</v>
       </c>
       <c r="G12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>87</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="K12" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="R12" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="R12" s="3" t="s">
+      <c r="S12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="T12" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="U12" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="V12" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Y12" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Z12" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AA12" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AB12" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AC12" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AD12" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AE12" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AF12" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG12" s="3" t="s">
         <v>138</v>
@@ -2462,64 +2462,64 @@
         <v>84</v>
       </c>
       <c r="G13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>87</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>143</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R13" s="3" t="s">
         <v>144</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>94</v>
+        <v>129</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="V13" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="W13" s="3" t="s">
         <v>145</v>
       </c>
       <c r="X13" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Y13" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AA13" s="3" t="s">
         <v>144</v>
@@ -2528,16 +2528,16 @@
         <v>144</v>
       </c>
       <c r="AC13" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AD13" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AE13" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AF13" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG13" s="3" t="s">
         <v>146</v>
@@ -2913,7 +2913,7 @@
     </row>
     <row r="4" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>352</v>
@@ -2934,7 +2934,7 @@
         <v>356</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>249</v>
@@ -2964,12 +2964,12 @@
         <v>359</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>360</v>
@@ -2990,7 +2990,7 @@
         <v>356</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>249</v>
@@ -3020,12 +3020,12 @@
         <v>359</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>361</v>
@@ -3046,7 +3046,7 @@
         <v>356</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>249</v>
@@ -3076,7 +3076,7 @@
         <v>359</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -3102,7 +3102,7 @@
         <v>356</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>249</v>
@@ -3132,12 +3132,12 @@
         <v>359</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>363</v>
@@ -3158,7 +3158,7 @@
         <v>356</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>249</v>
@@ -3188,7 +3188,7 @@
         <v>359</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -3214,7 +3214,7 @@
         <v>356</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>249</v>
@@ -3244,7 +3244,7 @@
         <v>359</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -3814,7 +3814,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="121.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="28.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28.42578125" bestFit="1" customWidth="1"/>
@@ -4009,7 +4009,7 @@
     </row>
     <row r="4" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>185</v>
@@ -4027,7 +4027,7 @@
         <v>189</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>190</v>
@@ -4057,7 +4057,7 @@
         <v>194</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R4" s="3" t="s">
         <v>195</v>
@@ -4071,7 +4071,7 @@
     </row>
     <row r="5" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>198</v>
@@ -4089,7 +4089,7 @@
         <v>189</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>190</v>
@@ -4119,7 +4119,7 @@
         <v>194</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R5" s="3" t="s">
         <v>195</v>
@@ -4133,7 +4133,7 @@
     </row>
     <row r="6" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>199</v>
@@ -4151,7 +4151,7 @@
         <v>189</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>190</v>
@@ -4181,7 +4181,7 @@
         <v>194</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R6" s="3" t="s">
         <v>195</v>
@@ -4213,7 +4213,7 @@
         <v>189</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>190</v>
@@ -4243,7 +4243,7 @@
         <v>194</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R7" s="3" t="s">
         <v>195</v>
@@ -4257,7 +4257,7 @@
     </row>
     <row r="8" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>201</v>
@@ -4275,7 +4275,7 @@
         <v>189</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>190</v>
@@ -4305,7 +4305,7 @@
         <v>194</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R8" s="3" t="s">
         <v>195</v>
@@ -4337,7 +4337,7 @@
         <v>189</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>190</v>
@@ -4367,7 +4367,7 @@
         <v>194</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R9" s="3" t="s">
         <v>195</v>
@@ -4916,7 +4916,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="39.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="36.5703125" bestFit="1" customWidth="1"/>
@@ -5081,161 +5081,161 @@
     </row>
     <row r="4" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>317</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>318</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>319</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5246,102 +5246,102 @@
         <v>320</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>321</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5352,49 +5352,49 @@
         <v>322</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
